--- a/results/momentum_rising_latest.xlsx
+++ b/results/momentum_rising_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A96"/>
+  <dimension ref="A1:A84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,665 +426,581 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TJGC</t>
+          <t>MTLS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EGHT</t>
+          <t>ABLV</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OUST</t>
+          <t>QTRX</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AUDC</t>
+          <t>FORM</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>KLAC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>AMPH</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARHS</t>
+          <t>GCL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VICR</t>
+          <t>MRNA</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SILC</t>
+          <t>RENX</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TNMG</t>
+          <t>FEAM</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>PRTH</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>VICR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AGEN</t>
+          <t>MYGN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OLLI</t>
+          <t>GRAL</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>YDES</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>P</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OESX</t>
+          <t>MRAM</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SGHT</t>
+          <t>NTRA</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FLXS</t>
+          <t>ASYS</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TAYD</t>
+          <t>REFR</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SECZ</t>
+          <t>TWAV</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CLMB</t>
+          <t>MXL</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>XXI</t>
+          <t>DMAC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LSCC</t>
+          <t>BNR</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>QMCO</t>
+          <t>AIFA</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>AAON</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>PDFS</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MYGN</t>
+          <t>GGR</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BATRA</t>
+          <t>KAZR</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>COHU</t>
+          <t>CRCT</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MRVI</t>
+          <t>SDEV</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PDFS</t>
+          <t>LGND</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ALNT</t>
+          <t>HQI</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IMOS</t>
+          <t>SECZ</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AMRX</t>
+          <t>SILC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MREO</t>
+          <t>SVRN</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>QTRX</t>
+          <t>SHPH</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DGII</t>
+          <t>NNBR</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FIRY</t>
+          <t>SGHT</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BHFAM</t>
+          <t>PSIG</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>ARQQ</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SAIH</t>
+          <t>SXTP</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ARQQ</t>
+          <t>XXI</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>OSUR</t>
+          <t>KBSX</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GLND</t>
+          <t>TAYD</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CRCT</t>
+          <t>EEIQ</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>HLP</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>MKTW</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LGND</t>
+          <t>QMCO</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AIXC</t>
+          <t>TKNO</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>DDOG</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BLFS</t>
+          <t>OESX</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MRAM</t>
+          <t>LTRX</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GGR</t>
+          <t>WSHP</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AIFA</t>
+          <t>PS</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BATRK</t>
+          <t>JWEL</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SONO</t>
+          <t>ILMN</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>AMRX</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>RGEN</t>
+          <t>SUIG</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FWDI</t>
+          <t>MQ</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MASS</t>
+          <t>LRCX</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>KBSX</t>
+          <t>COHU</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>USDE</t>
+          <t>MREO</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MLCI</t>
+          <t>EMBC</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>MLCI</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>IOSP</t>
+          <t>CLMB</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STKE</t>
+          <t>MASS</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>KLIC</t>
+          <t>RGEN</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>OLLI</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>REFR</t>
+          <t>AGEN</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>WSHP</t>
+          <t>ARHS</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>USDEW</t>
+          <t>LSCC</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SDEV</t>
+          <t>BAND</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>KMTS</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BNR</t>
+          <t>FIRY</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SVCO</t>
+          <t>MPWR</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MXL</t>
+          <t>TER</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>KLIC</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SHPH</t>
+          <t>ENTG</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PSIG</t>
+          <t>STKE</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PRTH</t>
+          <t>USDE</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TKNO</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>SXTP</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>KAZR</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>SUIG</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>LTRX</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>BLLN</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>FORM</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>ABLV</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>EEIQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>MRNA</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>DMAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>ONCO</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>SVRN</t>
+          <t>TJGC</t>
         </is>
       </c>
     </row>

--- a/results/momentum_rising_latest.xlsx
+++ b/results/momentum_rising_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A83"/>
+  <dimension ref="A1:A86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,350 +426,350 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SILC</t>
+          <t>P</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RXRX</t>
+          <t>RMBS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LFCR</t>
+          <t>OPTX</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLGL</t>
+          <t>NTNX</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LSCC</t>
+          <t>DMRC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>NTWK</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>KLIC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DLXY</t>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CRVO</t>
+          <t>VCTR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IMMP</t>
+          <t>LIND</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>COHU</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NVMI</t>
+          <t>CRVO</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VICR</t>
+          <t>ASYS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>AMPL</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BTLN</t>
+          <t>SSTI</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>XRPN</t>
+          <t>ICHR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>SHOP</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ICHR</t>
+          <t>NVMI</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>QSI</t>
+          <t>SYNA</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>IBRX</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SINT</t>
+          <t>NTAP</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>ON</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>OKTA</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>CBNK</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>INAB</t>
+          <t>MSGM</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FOSL</t>
+          <t>QLYS</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STKE</t>
+          <t>KRNT</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>AIFA</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IBRX</t>
+          <t>FOSL</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SYNA</t>
+          <t>DDOG</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>XRPNU</t>
+          <t>SNPS</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TJGC</t>
+          <t>PTC</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ENTG</t>
+          <t>ODD</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TLN</t>
+          <t>IMMP</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>SILC</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AIFA</t>
+          <t>REBN</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>CGNX</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AXTI</t>
+          <t>EVCM</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NAUT</t>
+          <t>III</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>TLN</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>ACLS</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>LSCC</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KLIC</t>
+          <t>TENB</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SSTI</t>
+          <t>PDFS</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FORM</t>
+          <t>NTCT</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>ABLV</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PDFS</t>
+          <t>LITE</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PACB</t>
+          <t>INAB</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PPLI</t>
+          <t>BIRD</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>SOTK</t>
         </is>
       </c>
     </row>
@@ -783,217 +783,238 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>COHU</t>
+          <t>SLGL</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>NAUT</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>QMCO</t>
+          <t>SANG</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MKSI</t>
+          <t>PAHC</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ANGI</t>
+          <t>NMAD</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>KOD</t>
+          <t>RELL</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ACLS</t>
+          <t>CRWD</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ASPS</t>
+          <t>IMOS</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>MRVL</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>AXTI</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>KOD</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>OCC</t>
+          <t>BTLN</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MASS</t>
+          <t>FEAM</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ASYS</t>
+          <t>PXS</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>PAYS</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>OPRX</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>KRNT</t>
+          <t>PANW</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>QMCO</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ABLV</t>
+          <t>SHLS</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MSGM</t>
+          <t>STKE</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ABSI</t>
+          <t>OCG</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>LFCR</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SANG</t>
+          <t>RXRX</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SEER</t>
+          <t>AHG</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CAMT</t>
+          <t>MDAI</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>ELMT</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PMVP</t>
+          <t>ENTG</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>REBN</t>
+          <t>AEHL</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>DLXY</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>OPTX</t>
+          <t>MKSI</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>RFAI</t>
+          <t>ENGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>AMAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PACB</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>AVPT</t>
         </is>
       </c>
     </row>

--- a/results/momentum_rising_latest.xlsx
+++ b/results/momentum_rising_latest.xlsx
@@ -426,203 +426,203 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SYNA</t>
+          <t>HPK</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KRNT</t>
+          <t>PAX</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>PRHI</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>HSTM</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>RPGL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PICS</t>
+          <t>SYNA</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>SYPR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>PTC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>SCHL</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TPCS</t>
+          <t>RGC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>HQWWW</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VALU</t>
+          <t>TP</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>GRDX</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ARTW</t>
+          <t>ATOS</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BGM</t>
+          <t>AMPL</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PAX</t>
+          <t>JG</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FVNNU</t>
+          <t>MAT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FLYW</t>
+          <t>JAKK</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LSAK</t>
+          <t>GTLB</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NAUT</t>
+          <t>AFRM</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>ENGS</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BMR</t>
+          <t>TEAM</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>INTR</t>
+          <t>RELL</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IRIX</t>
+          <t>SHOP</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>AGBK</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SHLS</t>
+          <t>MWYN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LCUT</t>
+          <t>OKTA</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>GIBO</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GIBO</t>
+          <t>ICG</t>
         </is>
       </c>
     </row>
@@ -636,364 +636,364 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RRGB</t>
+          <t>APEI</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BTLN</t>
+          <t>P</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>VAI</t>
+          <t>BTSGU</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>RRGB</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SBC</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FEBO</t>
+          <t>ASO</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>ARTW</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>FNKO</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ATOS</t>
+          <t>BGM</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SMXT</t>
+          <t>LIND</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BYRN</t>
+          <t>GCT</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>FLYW</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>IDAI</t>
+          <t>CHAD</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TENB</t>
+          <t>FEBO</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AHG</t>
+          <t>BMR</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PENG</t>
+          <t>TENB</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SCHL</t>
+          <t>NAUT</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TLN</t>
+          <t>LSAK</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>TW</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>FRSH</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>INTR</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NMAD</t>
+          <t>AHG</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>PRME</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>BRBI</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>NTSK</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>RELL</t>
+          <t>KRNT</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MWYN</t>
+          <t>PENG</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BTSG</t>
+          <t>NTAP</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>PICS</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>SHLS</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>QTEX</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PRME</t>
+          <t>ACB</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>HQWWW</t>
+          <t>BTLN</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BTSGU</t>
+          <t>NMAD</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>FVNNU</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PRHI</t>
+          <t>VALU</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>RGC</t>
+          <t>FTNT</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STNE</t>
+          <t>PDSB</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AGBK</t>
+          <t>IDAI</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>QTEX</t>
+          <t>BYRN</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SBC</t>
+          <t>SNPS</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>RPGL</t>
+          <t>STNE</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BRBI</t>
+          <t>BTSG</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FNKO</t>
+          <t>TPCS</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PDSB</t>
+          <t>RCEL</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ACB</t>
+          <t>SMXT</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>VAI</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>PAYS</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>OPCH</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CHAD</t>
+          <t>IRIX</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>LCUT</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SYPR</t>
+          <t>TLN</t>
         </is>
       </c>
     </row>

--- a/results/momentum_rising_latest.xlsx
+++ b/results/momentum_rising_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A83"/>
+  <dimension ref="A1:A79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,329 +426,329 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>ENGS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PAX</t>
+          <t>GCL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PRHI</t>
+          <t>SCHL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>ACIC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RPGL</t>
+          <t>PICS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SYNA</t>
+          <t>BGM</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SYPR</t>
+          <t>P</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>SHLS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCHL</t>
+          <t>AGBK</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RGC</t>
+          <t>RELL</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HQWWW</t>
+          <t>BYRN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TW</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>ZSQR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ATOS</t>
+          <t>HPK</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>GTLB</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>RPGL</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>SMXT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>RMCF</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>GCT</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>AMPL</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>TLN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>KRNT</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RELL</t>
+          <t>FRSH</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>AISP</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AGBK</t>
+          <t>TENB</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MWYN</t>
+          <t>PAX</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>SOTK</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GIBO</t>
+          <t>OKTA</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>APOG</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SOTK</t>
+          <t>TEAM</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>SUJA</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>BMR</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BTSGU</t>
+          <t>BRZE</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RRGB</t>
+          <t>RCEL</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SBC</t>
+          <t>JDZG</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>SNWV</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ARTW</t>
+          <t>FVNNU</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FNKO</t>
+          <t>GIBO</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BGM</t>
+          <t>DLO</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>HSTM</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>SWRD</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FLYW</t>
+          <t>PDSB</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CHAD</t>
+          <t>RZLT</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FEBO</t>
+          <t>SHOP</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BMR</t>
+          <t>NTSK</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TENB</t>
+          <t>FNKO</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NAUT</t>
+          <t>PGNY</t>
         </is>
       </c>
     </row>
@@ -762,238 +762,210 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>LCUT</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>NTAP</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>INTR</t>
+          <t>ENSC</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AHG</t>
+          <t>PRHI</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PRME</t>
+          <t>MAT</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BRBI</t>
+          <t>GRDX</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>APEI</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>KRNT</t>
+          <t>KNSA</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PENG</t>
+          <t>OPCH</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>FLYW</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PICS</t>
+          <t>SKK</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SHLS</t>
+          <t>ASO</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>QTEX</t>
+          <t>MWYN</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ACB</t>
+          <t>SKWD</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BTLN</t>
+          <t>ELOG</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NMAD</t>
+          <t>STNE</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FVNNU</t>
+          <t>INTR</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>VALU</t>
+          <t>MTEX</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>PENG</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PDSB</t>
+          <t>VAI</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>IDAI</t>
+          <t>IRIX</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BYRN</t>
+          <t>PTC</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>LIND</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STNE</t>
+          <t>OLB</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BTSG</t>
+          <t>ICG</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TPCS</t>
+          <t>CHAD</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>AFRM</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SMXT</t>
+          <t>HQWWW</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>VAI</t>
+          <t>AFRI</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PAYS</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>OPCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>IRIX</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>LCUT</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>TLN</t>
+          <t>PLTR</t>
         </is>
       </c>
     </row>

--- a/results/momentum_rising_latest.xlsx
+++ b/results/momentum_rising_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A79"/>
+  <dimension ref="A1:A82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,420 +426,420 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>SWRD</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>AHG</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCHL</t>
+          <t>ENGS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ACIC</t>
+          <t>HPK</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PICS</t>
+          <t>COR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BGM</t>
+          <t>FNKO</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>GCL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SHLS</t>
+          <t>TLN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AGBK</t>
+          <t>BYRN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RELL</t>
+          <t>RPGL</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BYRN</t>
+          <t>PENG</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>MAT</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ZSQR</t>
+          <t>CRAI</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>ARTW</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>APOG</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RPGL</t>
+          <t>MRNA</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SMXT</t>
+          <t>JVA</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RMCF</t>
+          <t>TENB</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>HEPS</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>OKTA</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TLN</t>
+          <t>PRDO</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>KRNT</t>
+          <t>BOLT</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>QDEL</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AISP</t>
+          <t>ELOG</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TENB</t>
+          <t>SKWD</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PAX</t>
+          <t>PLTR</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SOTK</t>
+          <t>BRBI</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>ENSC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>APOG</t>
+          <t>SEZL</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>AFYA</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SUJA</t>
+          <t>NRDS</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BMR</t>
+          <t>JG</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BRZE</t>
+          <t>TW</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>PGNY</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>GIBO</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SNWV</t>
+          <t>BMR</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FVNNU</t>
+          <t>SMXT</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GIBO</t>
+          <t>PDSB</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DLO</t>
+          <t>ASO</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>PAYS</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SWRD</t>
+          <t>JDZG</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PDSB</t>
+          <t>GTLB</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>RZLT</t>
+          <t>P</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>BLKB</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>PTC</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FNKO</t>
+          <t>MQ</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PGNY</t>
+          <t>ACIC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>LSAK</t>
+          <t>RELL</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>LCUT</t>
+          <t>SOTK</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>RCEL</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ENSC</t>
+          <t>NTSK</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PRHI</t>
+          <t>CRNC</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>APEI</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>INTR</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>TRI</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>KNSA</t>
+          <t>SPT</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>SHOP</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FLYW</t>
+          <t>NAUT</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SKK</t>
+          <t>PICS</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>AMPL</t>
         </is>
       </c>
     </row>
@@ -853,49 +853,49 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SKWD</t>
+          <t>STNE</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ELOG</t>
+          <t>AGBK</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STNE</t>
+          <t>LOCO</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>INTR</t>
+          <t>PRHI</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MTEX</t>
+          <t>PCTY</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PENG</t>
+          <t>NWE</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>VAI</t>
+          <t>INTA</t>
         </is>
       </c>
     </row>
@@ -909,63 +909,84 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>SUJA</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>BORR</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>OLB</t>
+          <t>ICG</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>BRZE</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CHAD</t>
+          <t>TEAM</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>OPCH</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>HQWWW</t>
+          <t>LSAK</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AFRI</t>
+          <t>PAX</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>PBYI</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>FRSH</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>DDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>HSTM</t>
         </is>
       </c>
     </row>

--- a/results/momentum_rising_latest.xlsx
+++ b/results/momentum_rising_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A82"/>
+  <dimension ref="A1:A66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,567 +426,455 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SWRD</t>
+          <t>AHCO</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AHG</t>
+          <t>ELOG</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>PCTY</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>EBAY</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>SJ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FNKO</t>
+          <t>MRNA</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>CTAS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TLN</t>
+          <t>ODD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BYRN</t>
+          <t>CCEP</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RPGL</t>
+          <t>COR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PENG</t>
+          <t>APA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>ASO</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CRAI</t>
+          <t>AIXI</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ARTW</t>
+          <t>QDEL</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>APOG</t>
+          <t>SUJA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>RELL</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JVA</t>
+          <t>JYD</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TENB</t>
+          <t>BOLT</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HEPS</t>
+          <t>AHG</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>PDSB</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PRDO</t>
+          <t>DCBO</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BOLT</t>
+          <t>TEAM</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>QDEL</t>
+          <t>OPLN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ELOG</t>
+          <t>KMRK</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SKWD</t>
+          <t>LIFE</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>SHOP</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BRBI</t>
+          <t>HEPS</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ENSC</t>
+          <t>ETSY</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SEZL</t>
+          <t>DSGX</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AFYA</t>
+          <t>BYRN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NRDS</t>
+          <t>MWYN</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>NTSK</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>AMPL</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PGNY</t>
+          <t>TRI</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GIBO</t>
+          <t>ZSQR</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BMR</t>
+          <t>KDP</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SMXT</t>
+          <t>HURN</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PDSB</t>
+          <t>ACIC</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>SPT</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>HPK</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>BMR</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>INTA</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>CRNC</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>LOCO</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>ENSC</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MQ</t>
+          <t>PCRX</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ACIC</t>
+          <t>BORR</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RELL</t>
+          <t>PICS</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SOTK</t>
+          <t>OPCH</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>EFOR</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>OTEX</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CRNC</t>
+          <t>CART</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>MQ</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>INTR</t>
+          <t>PROF</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>ENGS</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SPT</t>
+          <t>GCL</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>SMXT</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NAUT</t>
+          <t>JDZG</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PICS</t>
+          <t>RPGL</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>CRAI</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MWYN</t>
+          <t>NIQ</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STNE</t>
+          <t>AGBK</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AGBK</t>
+          <t>FLYE</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>LOCO</t>
+          <t>FRPT</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PRHI</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>PCTY</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>NWE</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>INTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>IRIX</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>SUJA</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>BORR</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>ICG</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>BRZE</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>TEAM</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>OPCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>LSAK</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>PAX</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>PBYI</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>FRSH</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>DDI</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>HSTM</t>
+          <t>BLKB</t>
         </is>
       </c>
     </row>

--- a/results/momentum_rising_latest.xlsx
+++ b/results/momentum_rising_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A66"/>
+  <dimension ref="A1:A53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,455 +426,364 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AHCO</t>
+          <t>CRNC</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ELOG</t>
+          <t>AHCO</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>CCEP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>SUJA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SJ</t>
+          <t>PICS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>FRPT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>HURN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ODD</t>
+          <t>CTAS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>FLYE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>OPCH</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>APEI</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>DCBO</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AIXI</t>
+          <t>EBAY</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>QDEL</t>
+          <t>ACIC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SUJA</t>
+          <t>BLKB</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RELL</t>
+          <t>ENGS</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JYD</t>
+          <t>OTEX</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BOLT</t>
+          <t>SMXT</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AHG</t>
+          <t>SLDE</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PDSB</t>
+          <t>SJ</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>JDZG</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>ETSY</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OPLN</t>
+          <t>KMRK</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>KMRK</t>
+          <t>NIQ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>HEPS</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>ASO</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HEPS</t>
+          <t>PCRX</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>TRI</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>HAS</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BYRN</t>
+          <t>COR</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MWYN</t>
+          <t>JYD</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>QDEL</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>ELOG</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>AIXI</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ZSQR</t>
+          <t>JG</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>ICG</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>BRBI</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ACIC</t>
+          <t>HSTM</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SPT</t>
+          <t>DSGX</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>ENSC</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BMR</t>
+          <t>GIBO</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>ODD</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CRNC</t>
+          <t>LOCO</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LOCO</t>
+          <t>HPK</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ENSC</t>
+          <t>PDSB</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PCRX</t>
+          <t>SHPH</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BORR</t>
+          <t>APA</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PICS</t>
+          <t>MRNA</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>EZPW</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>CART</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>PCTY</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CART</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>PROF</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>ENGS</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>GCL</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>SMXT</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>JDZG</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>RPGL</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>CRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>NIQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>AGBK</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>FLYE</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>FRPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>BLKB</t>
+          <t>ARQT</t>
         </is>
       </c>
     </row>

--- a/results/momentum_rising_latest.xlsx
+++ b/results/momentum_rising_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A53"/>
+  <dimension ref="A1:A80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,364 +426,553 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CRNC</t>
+          <t>PCRX</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AHCO</t>
+          <t>DSGX</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>SLDE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SUJA</t>
+          <t>PLMR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PICS</t>
+          <t>ATRC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FRPT</t>
+          <t>QDEL</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>OXSQ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>SUJA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FLYE</t>
+          <t>HPK</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>CHRD</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>FLYE</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>NIQ</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>FWRG</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ACIC</t>
+          <t>PRVA</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>EZPW</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>AHG</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>HAS</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SMXT</t>
+          <t>PCTY</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>LOCO</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SJ</t>
+          <t>BYRN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>PICS</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>CDW</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KMRK</t>
+          <t>FRPT</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>ETSY</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HEPS</t>
+          <t>EBAY</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>JG</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PCRX</t>
+          <t>AGYS</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>DBX</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>EFOR</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>ELOG</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>JYD</t>
+          <t>KDP</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>QDEL</t>
+          <t>APEI</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ELOG</t>
+          <t>ODD</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AIXI</t>
+          <t>ACHC</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>OPCH</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>CCEP</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BRBI</t>
+          <t>JYD</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>JDZG</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>CART</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ENSC</t>
+          <t>JZ</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GIBO</t>
+          <t>SMXT</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ODD</t>
+          <t>ASO</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LOCO</t>
+          <t>CCC</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>ENSC</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PDSB</t>
+          <t>SHPH</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SHPH</t>
+          <t>AGBK</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>HLP</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>AHCO</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EZPW</t>
+          <t>HURN</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>MWYN</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>HSTM</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>TRI</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>EXFY</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>CTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SMPL</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>GIBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>NVAX</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>NAVN</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>DCBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>GEHC</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PTLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>AIXI</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>KMRK</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>OTEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ACIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>CBRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>BIIB</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>CRNC</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>ARQT</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>COR</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ICG</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ENGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>CRVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>BLKB</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>BZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>MRNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>BRBI</t>
         </is>
       </c>
     </row>

--- a/results/momentum_rising_latest.xlsx
+++ b/results/momentum_rising_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A80"/>
+  <dimension ref="A1:A63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,553 +426,434 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PCRX</t>
+          <t>DCBO</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>ELOG</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>TRI</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PLMR</t>
+          <t>ODD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ATRC</t>
+          <t>NCPL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>QDEL</t>
+          <t>TCRT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OXSQ</t>
+          <t>FWRG</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SUJA</t>
+          <t>LOCO</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>PCTY</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CHRD</t>
+          <t>JG</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FLYE</t>
+          <t>PRVA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>MDLZ</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FWRG</t>
+          <t>RTSN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PRVA</t>
+          <t>MWYN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EZPW</t>
+          <t>CHRD</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AHG</t>
+          <t>FIZZ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>DSGX</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>GEHC</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LOCO</t>
+          <t>SLDE</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BYRN</t>
+          <t>TBCH</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PICS</t>
+          <t>PCRX</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>ARQT</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FRPT</t>
+          <t>ICG</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>APEI</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>SSEAU</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>HLP</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AGYS</t>
+          <t>CBRL</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DBX</t>
+          <t>ADP</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>HAS</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ELOG</t>
+          <t>AIXI</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>SMPL</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>ASO</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ODD</t>
+          <t>BMBL</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ACHC</t>
+          <t>HPK</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>BYRN</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>JZ</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>JYD</t>
+          <t>SKYA</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>ACIC</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>CTAS</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>JZ</t>
+          <t>BLKB</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SMXT</t>
+          <t>JDZG</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>ETSY</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CCC</t>
+          <t>ENGS</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ENSC</t>
+          <t>BLMN</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SHPH</t>
+          <t>PTLO</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AGBK</t>
+          <t>NAVN</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>JYD</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AHCO</t>
+          <t>LVLU</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>EMBC</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MWYN</t>
+          <t>COR</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>GIBO</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>CCC</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EXFY</t>
+          <t>AGBK</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>CTSH</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SMPL</t>
+          <t>CENTA</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GIBO</t>
+          <t>CCEP</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NVAX</t>
+          <t>AHG</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NAVN</t>
+          <t>PLMR</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>KDP</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>BZ</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>OTEX</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ADP</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>PTLO</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>AIXI</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>KMRK</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>OTEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>ACIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>CBRL</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>BIIB</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>CRNC</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>ARQT</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>COR</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>ICG</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>ENGS</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>CRVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>BLKB</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>BZ</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>MRNA</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>BRBI</t>
+          <t>EBAY</t>
         </is>
       </c>
     </row>

--- a/results/momentum_rising_latest.xlsx
+++ b/results/momentum_rising_latest.xlsx
@@ -426,56 +426,56 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>ADP</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ELOG</t>
+          <t>KDP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>JG</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ODD</t>
+          <t>FWRG</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>LOCO</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TCRT</t>
+          <t>PCRX</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FWRG</t>
+          <t>PTLO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LOCO</t>
+          <t>ETSY</t>
         </is>
       </c>
     </row>
@@ -489,56 +489,56 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>AGBK</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PRVA</t>
+          <t>OTEX</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MDLZ</t>
+          <t>APEI</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RTSN</t>
+          <t>MDLZ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MWYN</t>
+          <t>GIBO</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CHRD</t>
+          <t>ENGS</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FIZZ</t>
+          <t>AHG</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>ASO</t>
         </is>
       </c>
     </row>
@@ -552,308 +552,308 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>CTSH</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TBCH</t>
+          <t>HPK</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PCRX</t>
+          <t>CCC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>BLKB</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>DCBO</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>PLMR</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SSEAU</t>
+          <t>FIZZ</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>HAS</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CBRL</t>
+          <t>BLMN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>LVLU</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>NCPL</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AIXI</t>
+          <t>CTAS</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SMPL</t>
+          <t>ACIC</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>SMPL</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BMBL</t>
+          <t>BYRN</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>DSGX</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BYRN</t>
+          <t>TBCH</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>JZ</t>
+          <t>SKYA</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SKYA</t>
+          <t>CENTA</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ACIC</t>
+          <t>EMBC</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>SSEAU</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>BZ</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>AIXI</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>TRI</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>CBRL</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BLMN</t>
+          <t>JZ</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PTLO</t>
+          <t>PRVA</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NAVN</t>
+          <t>CHRD</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>JYD</t>
+          <t>NAVN</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>LVLU</t>
+          <t>SLDE</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>ARQT</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>TCRT</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GIBO</t>
+          <t>BMBL</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CCC</t>
+          <t>ICG</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AGBK</t>
+          <t>ODD</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>RTSN</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CENTA</t>
+          <t>HLP</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>ELOG</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AHG</t>
+          <t>MWYN</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PLMR</t>
+          <t>COR</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>EBAY</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>JDZG</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>CCEP</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>JYD</t>
         </is>
       </c>
     </row>

--- a/results/momentum_rising_latest.xlsx
+++ b/results/momentum_rising_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A63"/>
+  <dimension ref="A1:A74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,434 +426,511 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>RTSN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>HAS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>PRVA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FWRG</t>
+          <t>BLMN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SKYA</t>
+          <t>CBRL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SSNC</t>
+          <t>YSWY</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PLMR</t>
+          <t>DCBO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OLLI</t>
+          <t>JG</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MWYN</t>
+          <t>ROST</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EDHL</t>
+          <t>EXPE</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JYD</t>
+          <t>TRIP</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>FIZZ</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ARXS</t>
+          <t>MWYN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PCRX</t>
+          <t>HALO</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>BYRN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>YSWY</t>
+          <t>ODD</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>TBCH</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>ERIE</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>KMB</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>BRBR</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CHRD</t>
+          <t>APPF</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BMBL</t>
+          <t>SSNC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>STFS</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>CME</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>CAKE</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CBRL</t>
+          <t>ARQT</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TCRT</t>
+          <t>PTLO</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>FWRG</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CPOP</t>
+          <t>EXEL</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ACIC</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>JDZG</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AOUT</t>
+          <t>MRSH</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BYRN</t>
+          <t>NAVN</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SMPL</t>
+          <t>CCEP</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RGC</t>
+          <t>EDHL</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>TRI</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>ROP</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>CTSH</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>COKE</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FIZZ</t>
+          <t>MXCT</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>MNDY</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>JBDI</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TBCH</t>
+          <t>MGPI</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PTLO</t>
+          <t>RPRX</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>ETS</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>ETSY</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>IDXX</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>RGC</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>PCTY</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ODD</t>
+          <t>COST</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NAVN</t>
+          <t>MNST</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PFAI</t>
+          <t>BMBL</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>TCRT</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RTSN</t>
+          <t>SLDE</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>ENGS</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PRVA</t>
+          <t>INTU</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>JZ</t>
+          <t>JYD</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BLMN</t>
+          <t>FTRE</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>EXLS</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>ABNB</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CAKE</t>
+          <t>ASO</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>LYFT</t>
+          <t>OTEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SKYA</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>CASY</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>CHRD</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>HPK</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ACIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>CSGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>HUIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BLKB</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>APEI</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>KDP</t>
         </is>
       </c>
     </row>

--- a/results/momentum_rising_latest.xlsx
+++ b/results/momentum_rising_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A74"/>
+  <dimension ref="A1:A89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,511 +426,616 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RTSN</t>
+          <t>BYRN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>AMCR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PRVA</t>
+          <t>TBCH</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BLMN</t>
+          <t>RGC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CBRL</t>
+          <t>OTEX</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>YSWY</t>
+          <t>REAL</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>ARHS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>PCTY</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ROST</t>
+          <t>ABNB</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>AVTR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TRIP</t>
+          <t>HUIZ</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FIZZ</t>
+          <t>JDZG</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MWYN</t>
+          <t>KMB</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>BMBL</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BYRN</t>
+          <t>RPC</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ODD</t>
+          <t>MAZE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TBCH</t>
+          <t>ROP</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>INTU</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>FTRE</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BRBR</t>
+          <t>ADMA</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>APPF</t>
+          <t>EDHL</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SSNC</t>
+          <t>RTSN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STFS</t>
+          <t>ERIC</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>SKIN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CAKE</t>
+          <t>NAVN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>MRSH</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PTLO</t>
+          <t>IRLA</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FWRG</t>
+          <t>PTLE</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>JYD</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>ODD</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>ONC</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MRSH</t>
+          <t>PODD</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NAVN</t>
+          <t>INTA</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>EVER</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>EDHL</t>
+          <t>MTC</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>ENGS</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>BRCB</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>ROOT</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>ASO</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MXCT</t>
+          <t>PRGS</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MNDY</t>
+          <t>HAS</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>JBDI</t>
+          <t>SLDE</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>PRVA</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>RPRX</t>
+          <t>CNXC</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>CDZI</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>HALO</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IDXX</t>
+          <t>JBDI</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RGC</t>
+          <t>COKE</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>PAYX</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>EXEL</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>CSGP</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BMBL</t>
+          <t>CTSH</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TCRT</t>
+          <t>LOGI</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>EXLS</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>MAR</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>RPRX</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>JYD</t>
+          <t>ARQT</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>ADP</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>FIZZ</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>ERIE</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>JRVR</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>TRI</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SKYA</t>
+          <t>MNST</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CASY</t>
+          <t>DH</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CHRD</t>
+          <t>TCRT</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>STFS</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ACIC</t>
+          <t>EXPE</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>ICG</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>HUIZ</t>
+          <t>EBAY</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>ETSY</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>MNDY</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>SKYA</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>NRDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>MXCT</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SSNC</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>HCM</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>IIIV</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>DMRC</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>DCBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>APPF</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>BLKB</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>HLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>WTW</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>BRBR</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>APPN</t>
         </is>
       </c>
     </row>

--- a/results/momentum_rising_latest.xlsx
+++ b/results/momentum_rising_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A89"/>
+  <dimension ref="A1:A83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,616 +426,574 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BYRN</t>
+          <t>SIGI</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>MNDY</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TBCH</t>
+          <t>BRCB</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RGC</t>
+          <t>YSWY</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>BTOC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>TBCH</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARHS</t>
+          <t>RPRX</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>OTEX</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>INTU</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AVTR</t>
+          <t>PAYX</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HUIZ</t>
+          <t>ENGS</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>ORIC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>MRSH</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BMBL</t>
+          <t>ROP</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RPC</t>
+          <t>DMRC</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MAZE</t>
+          <t>PEPG</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>CME</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>ICG</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>TRIP</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ADMA</t>
+          <t>NRDS</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EDHL</t>
+          <t>ADP</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RTSN</t>
+          <t>MAZE</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ERIC</t>
+          <t>ERIE</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SKIN</t>
+          <t>WTW</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NAVN</t>
+          <t>CDZI</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MRSH</t>
+          <t>EXEL</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IRLA</t>
+          <t>OPK</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PTLE</t>
+          <t>BMBL</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JYD</t>
+          <t>BSVN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ODD</t>
+          <t>BLMN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ONC</t>
+          <t>DCBO</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PODD</t>
+          <t>LOGI</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>CNXC</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EVER</t>
+          <t>EXLS</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MTC</t>
+          <t>AVTR</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>NRIX</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BRCB</t>
+          <t>MXCT</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ROOT</t>
+          <t>TRI</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>INTA</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PRGS</t>
+          <t>JDZG</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>INDP</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>KPLT</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PRVA</t>
+          <t>TCRT</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CNXC</t>
+          <t>APPN</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CDZI</t>
+          <t>ENTX</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>PCTY</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>JBDI</t>
+          <t>ONC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>HAS</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>ETSY</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>PEP</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>ARHS</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>MAR</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>RGC</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>ETS</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>SBUX</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>RPRX</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>CSGP</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>KMB</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FIZZ</t>
+          <t>SKYA</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>RPC</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>JRVR</t>
+          <t>ARQT</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>SKIN</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>RTSN</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>NAVN</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TCRT</t>
+          <t>PRGS</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STFS</t>
+          <t>TW</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>ASO</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>SSNC</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>OLED</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>HUIZ</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MNDY</t>
+          <t>MICC</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SKYA</t>
+          <t>ROOT</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NRDS</t>
+          <t>FTRE</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MXCT</t>
+          <t>AMCR</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SSNC</t>
+          <t>JRVR</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>FTDR</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>CTSH</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>IIIV</t>
+          <t>BLKB</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>DH</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DMRC</t>
+          <t>STFS</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>LYFT</t>
+          <t>CHKP</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DCBO</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>APPF</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>BLKB</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>HLP</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>WTW</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>BRBR</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>APPN</t>
+          <t>HPK</t>
         </is>
       </c>
     </row>

--- a/results/momentum_rising_latest.xlsx
+++ b/results/momentum_rising_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A83"/>
+  <dimension ref="A1:A79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,231 +426,231 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SIGI</t>
+          <t>ROOT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MNDY</t>
+          <t>ADP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRCB</t>
+          <t>ETSY</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>YSWY</t>
+          <t>OTEX</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BTOC</t>
+          <t>CTSH</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TBCH</t>
+          <t>SBUX</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RPRX</t>
+          <t>FTDR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>ETS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>YSWY</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>JRVR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>STFS</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORIC</t>
+          <t>BMBL</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MRSH</t>
+          <t>OLED</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>ENGS</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DMRC</t>
+          <t>AVTR</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PEPG</t>
+          <t>APPN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>MXCT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>HALO</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TRIP</t>
+          <t>INDP</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NRDS</t>
+          <t>CME</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MAZE</t>
+          <t>HPK</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>JDZG</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>PEP</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CDZI</t>
+          <t>RPRX</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>ARHS</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OPK</t>
+          <t>ARQT</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BMBL</t>
+          <t>AMCR</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>ORIC</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BLMN</t>
+          <t>TBCH</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>HUIZ</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>ASO</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CNXC</t>
+          <t>BLMN</t>
         </is>
       </c>
     </row>
@@ -664,91 +664,91 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AVTR</t>
+          <t>OPK</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NRIX</t>
+          <t>BLKB</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MXCT</t>
+          <t>SKYA</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>PCTY</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>TRI</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>TCRT</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>INDP</t>
+          <t>FDBC</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KPLT</t>
+          <t>MICC</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TCRT</t>
+          <t>TRIP</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>DIBS</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ENTX</t>
+          <t>EXEL</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>SIGI</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ONC</t>
+          <t>SSNC</t>
         </is>
       </c>
     </row>
@@ -762,238 +762,210 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>PAYX</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>TW</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ARHS</t>
+          <t>LOGI</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>MAZE</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>RGC</t>
+          <t>ERIE</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>PRGS</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>BRCB</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>RPC</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>CHKP</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>ENTX</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SKYA</t>
+          <t>FVN</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>RPC</t>
+          <t>ICG</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>PTLE</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SKIN</t>
+          <t>NRDS</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>RTSN</t>
+          <t>BSVN</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NAVN</t>
+          <t>KPLT</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PRGS</t>
+          <t>MNDY</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>MRSH</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>CSGP</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SSNC</t>
+          <t>SKIN</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>DCBO</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>HUIZ</t>
+          <t>CDZI</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MICC</t>
+          <t>KMB</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ROOT</t>
+          <t>WTW</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>CNXC</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>RTSN</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>JRVR</t>
+          <t>FTRE</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FTDR</t>
+          <t>ROP</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>INTU</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BLKB</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>DH</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>STFS</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>CHKP</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>HPK</t>
+          <t>INTA</t>
         </is>
       </c>
     </row>

--- a/results/momentum_rising_latest.xlsx
+++ b/results/momentum_rising_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A79"/>
+  <dimension ref="A1:A104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,462 +426,462 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ROOT</t>
+          <t>JDZG</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>KMB</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>FTRE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>CAPS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>SBUX</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>TRI</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FTDR</t>
+          <t>CDW</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>HPK</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>YSWY</t>
+          <t>SIGI</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JRVR</t>
+          <t>STFS</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STFS</t>
+          <t>DGICB</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BMBL</t>
+          <t>KPLT</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>GDYN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>NAUT</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AVTR</t>
+          <t>FTDR</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>AEYE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MXCT</t>
+          <t>MBRX</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>KINS</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>INDP</t>
+          <t>BRZE</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ROP</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>OPRX</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>BRCB</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>FISV</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>PRGS</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RPRX</t>
+          <t>CME</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ARHS</t>
+          <t>DCBO</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>OMH</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>MNDY</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ORIC</t>
+          <t>ADP</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TBCH</t>
+          <t>CNXC</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HUIZ</t>
+          <t>NTWK</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>APPN</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BLMN</t>
+          <t>ETS</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>ALGN</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>OPK</t>
+          <t>ICG</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>HTFL</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SKYA</t>
+          <t>SVIAW</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>ENGS</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>AVTR</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TCRT</t>
+          <t>MANH</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FDBC</t>
+          <t>LIFE</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MICC</t>
+          <t>BETR</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TRIP</t>
+          <t>TRAX</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DIBS</t>
+          <t>GMAB</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>TEAM</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SIGI</t>
+          <t>EVAX</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SSNC</t>
+          <t>PGNY</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>WTW</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>CHKP</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>DAKT</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>RPD</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MAZE</t>
+          <t>SLN</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>BMBL</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PRGS</t>
+          <t>MTEX</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BRCB</t>
+          <t>BMGL</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>RPC</t>
+          <t>PAYX</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>MMSI</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ENTX</t>
+          <t>BSY</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FVN</t>
+          <t>MANE</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>RPC</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PTLE</t>
+          <t>OLED</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NRDS</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>AGIO</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>KPLT</t>
+          <t>AGYS</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MNDY</t>
+          <t>INTA</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MRSH</t>
+          <t>JRVR</t>
         </is>
       </c>
     </row>
@@ -895,77 +895,252 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SKIN</t>
+          <t>HQY</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>TBCH</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CDZI</t>
+          <t>YSWY</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>RPRX</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>NRDS</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CNXC</t>
+          <t>LZ</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>RTSN</t>
+          <t>DIBS</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>MRSH</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>CDZI</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>DOCU</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>PTLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>FDBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>INDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ERIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>BLKB</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>AMCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>HAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>AVPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>HALO</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>EXYN</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>GP</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>INGN</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>REVB</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>IRON</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>CTSH</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>FRSH</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>OPK</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>EXLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>OTEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>ARHS</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>SKYA</t>
         </is>
       </c>
     </row>

--- a/results/momentum_rising_latest.xlsx
+++ b/results/momentum_rising_latest.xlsx
@@ -426,21 +426,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>HTFL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>BLKB</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>GMAB</t>
         </is>
       </c>
     </row>
@@ -454,301 +454,301 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>HPK</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>APPN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>ARHS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>ENGS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SIGI</t>
+          <t>LIFE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STFS</t>
+          <t>AMCR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DGICB</t>
+          <t>BSY</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KPLT</t>
+          <t>NRDS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>REVB</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NAUT</t>
+          <t>FTRE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FTDR</t>
+          <t>MNDY</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AEYE</t>
+          <t>PAYX</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MBRX</t>
+          <t>FTDR</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KINS</t>
+          <t>RPD</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BRZE</t>
+          <t>RPRX</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>AVPT</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>FDBC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BRCB</t>
+          <t>OPK</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>JRVR</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PRGS</t>
+          <t>OTEX</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>RPC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>AVTR</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OMH</t>
+          <t>DAKT</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MNDY</t>
+          <t>PGNY</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>ALGN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CNXC</t>
+          <t>SKYA</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>MMSI</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>DIBS</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>MTEX</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ALGN</t>
+          <t>BETR</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>TW</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>GDYN</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SVIAW</t>
+          <t>TRI</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>BMBL</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AVTR</t>
+          <t>DGICB</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>AEYE</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>CME</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BETR</t>
+          <t>PTLE</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TRAX</t>
+          <t>DOCU</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>PCTY</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>FRSH</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EVAX</t>
+          <t>SPT</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PGNY</t>
+          <t>MANH</t>
         </is>
       </c>
     </row>
@@ -762,385 +762,385 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>TRAX</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DAKT</t>
+          <t>PRGS</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>RPD</t>
+          <t>LZ</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SLN</t>
+          <t>ICG</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BMBL</t>
+          <t>OMH</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MTEX</t>
+          <t>EXLS</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BMGL</t>
+          <t>DCBO</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>BMGL</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MMSI</t>
+          <t>KMB</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>TBCH</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MANE</t>
+          <t>ERIE</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>RPC</t>
+          <t>OPRX</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>SBUX</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>SIGI</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AGYS</t>
+          <t>CDZI</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>NAUT</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>JRVR</t>
+          <t>SLE</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>ADP</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HQY</t>
+          <t>YSWY</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TBCH</t>
+          <t>CTSH</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>YSWY</t>
+          <t>INDP</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>RPRX</t>
+          <t>OLED</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NRDS</t>
+          <t>MBRX</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>SVIAW</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DIBS</t>
+          <t>STFS</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MRSH</t>
+          <t>JDZG</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CDZI</t>
+          <t>TEAM</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>GP</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PTLE</t>
+          <t>AGIO</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FDBC</t>
+          <t>NTWK</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SLE</t>
+          <t>KPLT</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>INDP</t>
+          <t>HAS</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>EXYN</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>INTA</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>ETS</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>FISV</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>HALO</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>BRCB</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>ROP</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EXYN</t>
+          <t>SLN</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>GP</t>
+          <t>INGN</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>INGN</t>
+          <t>BRZE</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>REVB</t>
+          <t>CNXC</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>HQY</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>MANE</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>CSGP</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>OPK</t>
+          <t>INTU</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>MRSH</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>IRON</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>EVAX</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>KINS</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SPT</t>
+          <t>CHKP</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ARHS</t>
+          <t>AGYS</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SKYA</t>
+          <t>CDW</t>
         </is>
       </c>
     </row>

--- a/results/momentum_rising_latest.xlsx
+++ b/results/momentum_rising_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A104"/>
+  <dimension ref="A1:A158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,560 +426,560 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>BOTJ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>HURN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>OZK</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAPS</t>
+          <t>ATGL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>FITB</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>CFFI</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARHS</t>
+          <t>PCTY</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>GMAB</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>AGIO</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>KPLT</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>SKYA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NRDS</t>
+          <t>OSPN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>REVB</t>
+          <t>TACT</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>AMRX</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MNDY</t>
+          <t>ACIW</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>OPK</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FTDR</t>
+          <t>ATRC</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RPD</t>
+          <t>XLAB</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RPRX</t>
+          <t>CLBT</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>INTA</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FDBC</t>
+          <t>HPK</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OPK</t>
+          <t>ARHS</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JRVR</t>
+          <t>TLS</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>EFOR</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RPC</t>
+          <t>DSGX</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AVTR</t>
+          <t>ENGS</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DAKT</t>
+          <t>SEPN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PGNY</t>
+          <t>AVTR</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ALGN</t>
+          <t>EMBC</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SKYA</t>
+          <t>AVPT</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MMSI</t>
+          <t>TBCH</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DIBS</t>
+          <t>ASBH</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MTEX</t>
+          <t>MITK</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BETR</t>
+          <t>SGRY</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BMGL</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>AMCR</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>DOX</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BMBL</t>
+          <t>BVS</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DGICB</t>
+          <t>SLN</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AEYE</t>
+          <t>JAKK</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>CTAS</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PTLE</t>
+          <t>CERT</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>FTDR</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>MORN</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>MYGN</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SPT</t>
+          <t>APPN</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>ASRV</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>BIIB</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TRAX</t>
+          <t>MANH</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PRGS</t>
+          <t>HON</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>ICLR</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>OMH</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>OMH</t>
+          <t>STFS</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>CNXC</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>NCNO</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BMGL</t>
+          <t>TRAX</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>EPSN</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TBCH</t>
+          <t>AGNT</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>NDAQ</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>SIBN</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>AGYS</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>FRSH</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SIGI</t>
+          <t>SFNC</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CDZI</t>
+          <t>PBYI</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>NAUT</t>
+          <t>NSSC</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SLE</t>
+          <t>IRTC</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>CZFS</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>YSWY</t>
+          <t>PRGS</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>HTFL</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>INDP</t>
+          <t>POOL</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>ABLV</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MBRX</t>
+          <t>HQY</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SVIAW</t>
+          <t>ANDG</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STFS</t>
+          <t>NTWK</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>MMSI</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>AMPL</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>GP</t>
+          <t>DCOM</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>DMAC</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>CWST</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>KPLT</t>
+          <t>GRDX</t>
         </is>
       </c>
     </row>
@@ -993,42 +993,42 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EXYN</t>
+          <t>INDB</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>MBRX</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>MNDY</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>HALO</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>FNLC</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BRCB</t>
+          <t>BSY</t>
         </is>
       </c>
     </row>
@@ -1042,103 +1042,481 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SLN</t>
+          <t>DIBS</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>INGN</t>
+          <t>INDP</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BRZE</t>
+          <t>GP</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CNXC</t>
+          <t>NIQ</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>HQY</t>
+          <t>DOCU</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MANE</t>
+          <t>FTRE</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>LZ</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>CDLR</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MRSH</t>
+          <t>LFST</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>BL</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EVAX</t>
+          <t>AVAH</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>KINS</t>
+          <t>RENT</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>REVB</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AGYS</t>
+          <t>BRZE</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
+        <is>
+          <t>FDBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>CDZI</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>DBX</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>SGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>RPD</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>CHKP</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>CBNK</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>BETR</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>EXYN</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>RPC</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>CME</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>INGN</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>PAA</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>YSWY</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>FIVN</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>CENTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>SIGI</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>ORRF</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>SLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>ASND</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>RPRX</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>SBUX</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>KLRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>KINS</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>SGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>ALRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>MANE</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>DGICB</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>IRON</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>TRI</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>OPRX</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>CENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>OLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>BLKB</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>COO</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>SAIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>BRCB</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>OTEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>JJSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>CINF</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>KXIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>MTEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>ICG</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>UTHR</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>GDYN</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>HCSG</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>CAPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>CVBF</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>DAKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>LKFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
         <is>
           <t>CDW</t>
         </is>

--- a/results/momentum_rising_latest.xlsx
+++ b/results/momentum_rising_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A158"/>
+  <dimension ref="A1:A99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,1099 +426,686 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BOTJ</t>
+          <t>CCB</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>HAS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OZK</t>
+          <t>ALRM</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>SGP</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>POWW</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>NTWK</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>EPSN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>OZK</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>FIVN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KPLT</t>
+          <t>ESLA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SKYA</t>
+          <t>CENT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OSPN</t>
+          <t>ROP</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TACT</t>
+          <t>MTLS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AMRX</t>
+          <t>NWE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ACIW</t>
+          <t>SAGT</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OPK</t>
+          <t>POOL</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ATRC</t>
+          <t>FIBK</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>XLAB</t>
+          <t>KRRO</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CLBT</t>
+          <t>COLB</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>SWIM</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>KELYB</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ARHS</t>
+          <t>EXYN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TLS</t>
+          <t>SIGI</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>CHKP</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>QLYS</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>RDWR</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SEPN</t>
+          <t>AMRX</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AVTR</t>
+          <t>BRCB</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>GRDX</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>ATGL</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TBCH</t>
+          <t>CERT</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ASBH</t>
+          <t>FCNCA</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MITK</t>
+          <t>GMAB</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SGRY</t>
+          <t>RPRX</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BMGL</t>
+          <t>TROO</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>DSP</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>SEPN</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BVS</t>
+          <t>KXIN</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SLN</t>
+          <t>FTRE</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>CHMG</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>AVPT</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>CDZI</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FTDR</t>
+          <t>INVE</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MORN</t>
+          <t>BBT</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MYGN</t>
+          <t>SGRY</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>ELMT</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ASRV</t>
+          <t>OCTV</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>OMH</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>SLN</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>BOTJ</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>JAKK</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>OMH</t>
+          <t>TLS</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STFS</t>
+          <t>RENT</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CNXC</t>
+          <t>MYGN</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NCNO</t>
+          <t>DIBS</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TRAX</t>
+          <t>INDP</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EPSN</t>
+          <t>BSIN</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AGNT</t>
+          <t>EMBC</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>NTSK</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SIBN</t>
+          <t>RPD</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AGYS</t>
+          <t>INGN</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>CZFS</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SFNC</t>
+          <t>YSWY</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PBYI</t>
+          <t>CENTA</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>NSSC</t>
+          <t>ASTL</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>IRTC</t>
+          <t>ANIK</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CZFS</t>
+          <t>CLAR</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PRGS</t>
+          <t>TENB</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>RCEL</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>OLED</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ABLV</t>
+          <t>BRZE</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>HQY</t>
+          <t>ENGS</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ANDG</t>
+          <t>PLSE</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>NDAQ</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MMSI</t>
+          <t>MGRT</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>SAIL</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DCOM</t>
+          <t>MEDP</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DMAC</t>
+          <t>HCSG</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CWST</t>
+          <t>HURN</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>BMGL</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>FNLC</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>INDB</t>
+          <t>TACT</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MBRX</t>
+          <t>LFST</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MNDY</t>
+          <t>IRTC</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>CGNT</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FNLC</t>
+          <t>ATRC</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>ORRF</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>TRAX</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DIBS</t>
+          <t>NSIT</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>INDP</t>
+          <t>BETR</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>GP</t>
+          <t>KPLT</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>IRON</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>OSPN</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>MANE</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>CINF</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CDLR</t>
+          <t>HTFL</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>LFST</t>
+          <t>SAIC</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BL</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>AVAH</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>RENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>REVB</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>BRZE</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>FDBC</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>CDZI</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>TW</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>DBX</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>SGHT</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>RPD</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>CHKP</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>CBNK</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>BETR</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>EXYN</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>RPC</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>CME</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>INGN</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>HOPE</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>PAA</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>YSWY</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>FIVN</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>CENTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>SIGI</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>ORRF</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>SLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>ASND</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>RPRX</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>SBUX</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>KLRA</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>KINS</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>SGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>ALRM</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>MANE</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>DGICB</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>IRON</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>TRI</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>OPRX</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>CENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>BLKB</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>COO</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>SAIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>BRCB</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>OTEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>JJSF</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>CINF</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>KXIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>MTEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>ICG</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>UTHR</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>GDYN</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>HCSG</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>CAPS</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>CVBF</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>DAKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>LKFT</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>CDW</t>
+          <t>MOBI</t>
         </is>
       </c>
     </row>

--- a/results/momentum_rising_latest.xlsx
+++ b/results/momentum_rising_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A99"/>
+  <dimension ref="A1:A118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,686 +426,819 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CCB</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>FSBC</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>BETR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SGP</t>
+          <t>CLAR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>POWW</t>
+          <t>XFOR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>INDP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EPSN</t>
+          <t>QLYS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OZK</t>
+          <t>MGRC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FIVN</t>
+          <t>SNES</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ESLA</t>
+          <t>EGBN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CENT</t>
+          <t>ELMT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>IRTC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>SWIM</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NWE</t>
+          <t>ATER</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SAGT</t>
+          <t>ALRM</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>CZNC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FIBK</t>
+          <t>RCEL</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KRRO</t>
+          <t>ROP</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>COLB</t>
+          <t>BMGL</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SWIM</t>
+          <t>SKYA</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>KELYB</t>
+          <t>PLSE</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EXYN</t>
+          <t>SLN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SIGI</t>
+          <t>RENT</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>OSPN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>QLYS</t>
+          <t>BBT</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>RDWR</t>
+          <t>NTSK</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AMRX</t>
+          <t>JAKK</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BRCB</t>
+          <t>SGRY</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>DSP</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>RDWR</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>NDAQ</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FCNCA</t>
+          <t>TRAX</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>SAIC</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RPRX</t>
+          <t>RDVT</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TROO</t>
+          <t>ABVC</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DSP</t>
+          <t>SBUX</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SEPN</t>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>KXIN</t>
+          <t>CCB</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>STAK</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CHMG</t>
+          <t>ESLA</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>TACT</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CDZI</t>
+          <t>MANE</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>INVE</t>
+          <t>AGIO</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BBT</t>
+          <t>CHKP</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SGRY</t>
+          <t>SAIL</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ELMT</t>
+          <t>LKFT</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>OCTV</t>
+          <t>BRCB</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>OMH</t>
+          <t>NTWK</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SLN</t>
+          <t>NWFL</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BOTJ</t>
+          <t>PHAR</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>BLLN</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TLS</t>
+          <t>ATGL</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>RENT</t>
+          <t>SWKS</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MYGN</t>
+          <t>BSIN</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DIBS</t>
+          <t>SHOE</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>INDP</t>
+          <t>GIBO</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BSIN</t>
+          <t>DOO</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>CERT</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>CGNT</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>RPD</t>
+          <t>ESQ</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>INGN</t>
+          <t>CINF</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CZFS</t>
+          <t>HAS</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>YSWY</t>
+          <t>BRZE</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CENTA</t>
+          <t>KMTS</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ASTL</t>
+          <t>SGP</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ANIK</t>
+          <t>SIBN</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CLAR</t>
+          <t>PRCT</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TENB</t>
+          <t>NWE</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>RPD</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>FTRE</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BRZE</t>
+          <t>KXIN</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>DIBS</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PLSE</t>
+          <t>ASND</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>TNDM</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MGRT</t>
+          <t>ASTL</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>ANIK</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>AVPT</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>HCSG</t>
+          <t>AMPL</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>IRON</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BMGL</t>
+          <t>HLP</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FNLC</t>
+          <t>SGHT</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TACT</t>
+          <t>PDLB</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>LFST</t>
+          <t>AMRX</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>IRTC</t>
+          <t>KPLT</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CGNT</t>
+          <t>TLS</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ATRC</t>
+          <t>MGRT</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ORRF</t>
+          <t>CDZI</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TRAX</t>
+          <t>KRRO</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>GRDX</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BETR</t>
+          <t>CART</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>KPLT</t>
+          <t>MYGN</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>HTFL</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>OSPN</t>
+          <t>ATRC</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MANE</t>
+          <t>STAA</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>CBFV</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>SEPN</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>RPRX</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>PYPD</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ENGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>PACB</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>CSX</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>NSSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>IMC</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>GMAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>FCNCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>LFST</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>SAGT</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>INGN</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>MEDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>CFFI</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
           <t>MOBI</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>SIGI</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>FIVN</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>OCTV</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>HALO</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>OLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>TENB</t>
         </is>
       </c>
     </row>

--- a/results/momentum_rising_latest.xlsx
+++ b/results/momentum_rising_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A118"/>
+  <dimension ref="A1:A141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,448 +426,448 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>ATGL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FSBC</t>
+          <t>ASND</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BETR</t>
+          <t>HTFL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CLAR</t>
+          <t>SNES</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>XFOR</t>
+          <t>ASTL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>INDP</t>
+          <t>PACB</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>QLYS</t>
+          <t>BMGL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MGRC</t>
+          <t>SIBN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SNES</t>
+          <t>EGBN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EGBN</t>
+          <t>GIBO</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ELMT</t>
+          <t>MAYS</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IRTC</t>
+          <t>CARL</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SWIM</t>
+          <t>NTSK</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ATER</t>
+          <t>IRTC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>TRAX</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CZNC</t>
+          <t>CAI</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>LMRI</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>MEDP</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BMGL</t>
+          <t>FCNCA</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SKYA</t>
+          <t>BRCB</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PLSE</t>
+          <t>DIBS</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SLN</t>
+          <t>MOBI</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RENT</t>
+          <t>TRMD</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OSPN</t>
+          <t>CERT</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BBT</t>
+          <t>QSI</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>TACT</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>ENGS</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SGRY</t>
+          <t>KVHI</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DSP</t>
+          <t>RCEL</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RDWR</t>
+          <t>INDP</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>LKFT</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TRAX</t>
+          <t>MRVI</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>PNRG</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>PHAR</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ABVC</t>
+          <t>NUTX</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>JLHL</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>BSIN</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CCB</t>
+          <t>PYPD</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STAK</t>
+          <t>QLYS</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ESLA</t>
+          <t>SBUX</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TACT</t>
+          <t>SIGI</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MANE</t>
+          <t>CTKB</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>ALRM</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>ALMR</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>SEPN</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LKFT</t>
+          <t>BOLT</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BRCB</t>
+          <t>OZK</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>JYD</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NWFL</t>
+          <t>STFS</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PHAR</t>
+          <t>GRAL</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BLLN</t>
+          <t>ENVX</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>EFOI</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>NOVTU</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BSIN</t>
+          <t>NOVT</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SHOE</t>
+          <t>NSSC</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GIBO</t>
+          <t>ATRC</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DOO</t>
+          <t>ANIX</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>POOL</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CGNT</t>
+          <t>PRCT</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>XFOR</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>TMCI</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>GMAB</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BRZE</t>
+          <t>AIOK</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>KMTS</t>
+          <t>AMAL</t>
         </is>
       </c>
     </row>
@@ -881,362 +881,523 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SIBN</t>
+          <t>KRRO</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PRCT</t>
+          <t>IMC</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>NWE</t>
+          <t>FBLA</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>RPD</t>
+          <t>KPLT</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>CFFI</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>KXIN</t>
+          <t>IRON</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DIBS</t>
+          <t>ORKA</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ASND</t>
+          <t>PTEN</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TNDM</t>
+          <t>ANIK</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ASTL</t>
+          <t>HLP</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ANIK</t>
+          <t>SAIC</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>NDAQ</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>RENT</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>PLUR</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>RIBBU</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SGHT</t>
+          <t>AVBC</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PDLB</t>
+          <t>BETR</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AMRX</t>
+          <t>FRBA</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>KPLT</t>
+          <t>PLSE</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TLS</t>
+          <t>REAL</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MGRT</t>
+          <t>ATER</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CDZI</t>
+          <t>SWKS</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>KRRO</t>
+          <t>TLS</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>DGII</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>FGBI</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MYGN</t>
+          <t>DOO</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>STAA</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ATRC</t>
+          <t>SWIM</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STAA</t>
+          <t>GH</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CBFV</t>
+          <t>SGRY</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SEPN</t>
+          <t>INM</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>RPRX</t>
+          <t>HAS</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PYPD</t>
+          <t>MYGN</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>NTWK</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PACB</t>
+          <t>KMTS</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>SLN</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>NSSC</t>
+          <t>FLWS</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>IMC</t>
+          <t>ERIC</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>ESQ</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FCNCA</t>
+          <t>MGRT</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>LFST</t>
+          <t>JAKK</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SAGT</t>
+          <t>FSBC</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>INGN</t>
+          <t>CLAR</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>PDLB</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>AVPT</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MOBI</t>
+          <t>BLLN</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SIGI</t>
+          <t>CHMG</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FIVN</t>
+          <t>CDZI</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>OCTV</t>
+          <t>SAGT</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>RDWR</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>ITRI</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
+        <is>
+          <t>PRPL</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>LFST</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>MANE</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>SHOE</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>IVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>LEGN</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>TNDM</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>ELMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>BRZE</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>INGN</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>REF</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>AMRX</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>RICK</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>KXIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>GNSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>AIFA</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>BVC</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>COAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>SGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>NBTX</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>HYNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>BSRR</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>HALO</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
         <is>
           <t>TENB</t>
         </is>

--- a/results/momentum_rising_latest.xlsx
+++ b/results/momentum_rising_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A141"/>
+  <dimension ref="A1:A99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,980 +426,686 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>TGTX</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ASND</t>
+          <t>REAL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>GIBO</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SNES</t>
+          <t>DMRC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ASTL</t>
+          <t>EFOI</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PACB</t>
+          <t>STAA</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BMGL</t>
+          <t>COAG</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SIBN</t>
+          <t>AFRI</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EGBN</t>
+          <t>BETR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GIBO</t>
+          <t>CLAR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MAYS</t>
+          <t>RIBBU</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CARL</t>
+          <t>FIVE</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>KPLT</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IRTC</t>
+          <t>DIBS</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TRAX</t>
+          <t>GNSS</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CAI</t>
+          <t>SWIM</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LMRI</t>
+          <t>TACT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>HLP</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FCNCA</t>
+          <t>OPRT</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BRCB</t>
+          <t>DOO</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DIBS</t>
+          <t>APOG</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MOBI</t>
+          <t>ATEX</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SGRY</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>PRPL</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>QSI</t>
+          <t>ENGS</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TACT</t>
+          <t>AIOK</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>ASND</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>KVHI</t>
+          <t>ORKA</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>IBG</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>INDP</t>
+          <t>TMCI</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LKFT</t>
+          <t>ATGL</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MRVI</t>
+          <t>POOL</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PNRG</t>
+          <t>ICON</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PHAR</t>
+          <t>AVBC</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>CHOW</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>JLHL</t>
+          <t>GLSI</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BSIN</t>
+          <t>SIGI</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PYPD</t>
+          <t>FGBI</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>QLYS</t>
+          <t>CTKB</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>PLUR</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SIGI</t>
+          <t>LUNG</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CTKB</t>
+          <t>KRRO</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>CHSN</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ALMR</t>
+          <t>LVO</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SEPN</t>
+          <t>PTEN</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BOLT</t>
+          <t>LKFT</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>OZK</t>
+          <t>TENB</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>JYD</t>
+          <t>SGHT</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STFS</t>
+          <t>ROP</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>LULU</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ENVX</t>
+          <t>REPL</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EFOI</t>
+          <t>BMGL</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NOVTU</t>
+          <t>AVPT</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NOVT</t>
+          <t>KXIN</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NSSC</t>
+          <t>ATER</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ATRC</t>
+          <t>SAIC</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ANIX</t>
+          <t>ERIC</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>PHAR</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PRCT</t>
+          <t>ALRM</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>XFOR</t>
+          <t>TRMD</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TMCI</t>
+          <t>BRCB</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>NXPI</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AIOK</t>
+          <t>PDLB</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AMAL</t>
+          <t>RJET</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SGP</t>
+          <t>KVHI</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>KRRO</t>
+          <t>PNRG</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>IMC</t>
+          <t>HYNE</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FBLA</t>
+          <t>GMAB</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>KPLT</t>
+          <t>SEPN</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>MLTX</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>AMRX</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ORKA</t>
+          <t>CHMG</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PTEN</t>
+          <t>IMC</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ANIK</t>
+          <t>HALO</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>KOD</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>RCEL</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>MOBI</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>RENT</t>
+          <t>LFST</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PLUR</t>
+          <t>HWKN</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>RIBBU</t>
+          <t>RIGL</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AVBC</t>
+          <t>ADMA</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BETR</t>
+          <t>FFTT</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FRBA</t>
+          <t>SNES</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PLSE</t>
+          <t>XNCR</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>CZWI</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ATER</t>
+          <t>JLHL</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>SGP</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TLS</t>
+          <t>ITRI</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DGII</t>
+          <t>GDYN</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FGBI</t>
+          <t>STFS</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DOO</t>
+          <t>IRON</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STAA</t>
+          <t>GRFS</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SWIM</t>
+          <t>LEGN</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>MYGN</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SGRY</t>
+          <t>NDAQ</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>INM</t>
+          <t>BVC</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>MANE</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MYGN</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>NTWK</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>KMTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
           <t>SLN</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>FLWS</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>ERIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>ESQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>MGRT</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>JAKK</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>FSBC</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>CLAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>PDLB</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>AVPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>BLLN</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>CHMG</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>CDZI</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>SAGT</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>RDWR</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>ITRI</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>PRPL</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>LFST</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>MANE</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>SHOE</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>IVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>LEGN</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>TNDM</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>ELMT</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>BRZE</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>INGN</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>REF</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>AMRX</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>RICK</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>KXIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>GNSS</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>AIFA</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>BVC</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>COAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>SGHT</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>NBTX</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>HYNE</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>BSRR</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>HALO</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>TENB</t>
         </is>
       </c>
     </row>

--- a/results/momentum_rising_latest.xlsx
+++ b/results/momentum_rising_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A99"/>
+  <dimension ref="A1:A80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,294 +426,294 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TGTX</t>
+          <t>SUNB</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>INM</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GIBO</t>
+          <t>ICON</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DMRC</t>
+          <t>KRRO</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EFOI</t>
+          <t>PNRG</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STAA</t>
+          <t>TENB</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COAG</t>
+          <t>ERIC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AFRI</t>
+          <t>SPCB</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BETR</t>
+          <t>SAIC</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CLAR</t>
+          <t>NXPI</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RIBBU</t>
+          <t>AVBC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>STFS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KPLT</t>
+          <t>NORD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DIBS</t>
+          <t>GIBO</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GNSS</t>
+          <t>KYMR</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SWIM</t>
+          <t>BETR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TACT</t>
+          <t>AIOK</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>RIBBU</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OPRT</t>
+          <t>DOO</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DOO</t>
+          <t>SGP</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>APOG</t>
+          <t>EFOI</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ATEX</t>
+          <t>PLUR</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SGRY</t>
+          <t>BRCB</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PRPL</t>
+          <t>FIVE</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>OPRT</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AIOK</t>
+          <t>ENGS</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ASND</t>
+          <t>RICK</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ORKA</t>
+          <t>ATEX</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IBG</t>
+          <t>HYNE</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TMCI</t>
+          <t>RIGL</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>SWIM</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>ATGL</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ICON</t>
+          <t>STAA</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AVBC</t>
+          <t>PTEN</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CHOW</t>
+          <t>XFOR</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GLSI</t>
+          <t>COAG</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SIGI</t>
+          <t>TRMD</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FGBI</t>
+          <t>BMGL</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CTKB</t>
+          <t>GDYN</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PLUR</t>
+          <t>BOLT</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>LUNG</t>
+          <t>PHAR</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KRRO</t>
+          <t>KXIN</t>
         </is>
       </c>
     </row>
@@ -727,385 +727,252 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LVO</t>
+          <t>TGTX</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PTEN</t>
+          <t>JLHL</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LKFT</t>
+          <t>CLAR</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TENB</t>
+          <t>RJET</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SGHT</t>
+          <t>HALO</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>NDAQ</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>AVPT</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>REPL</t>
+          <t>FGBI</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BMGL</t>
+          <t>GRFS</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>PDLB</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>KXIN</t>
+          <t>CTKB</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ATER</t>
+          <t>ORKA</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>DMRC</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ERIC</t>
+          <t>SNES</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PHAR</t>
+          <t>XNCR</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>CHOW</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>IMC</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BRCB</t>
+          <t>DHCNL</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>GMAB</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PDLB</t>
+          <t>REAL</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>RJET</t>
+          <t>SGRY</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>KVHI</t>
+          <t>LULU</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PNRG</t>
+          <t>ROP</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>HYNE</t>
+          <t>FFTT</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>HLP</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SEPN</t>
+          <t>KPLT</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MLTX</t>
+          <t>ITRI</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AMRX</t>
+          <t>POOL</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CHMG</t>
+          <t>DIBS</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>IMC</t>
+          <t>REPL</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>HWKN</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>KOD</t>
+          <t>AMRX</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>ATER</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MOBI</t>
+          <t>KOD</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>LFST</t>
+          <t>MAYS</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>HWKN</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>RIGL</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>ADMA</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>FFTT</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>SNES</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>XNCR</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>CZWI</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>JLHL</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>SGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>ITRI</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>GDYN</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>STFS</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>IRON</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>GRFS</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>LEGN</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>MYGN</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>NDAQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>BVC</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>MANE</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>SLN</t>
+          <t>LUNG</t>
         </is>
       </c>
     </row>
